--- a/光伏配储项目/电价数据/2026/格物站.xlsx
+++ b/光伏配储项目/电价数据/2026/格物站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.52198</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38462</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7641699999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.58641</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5798300000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52071</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.53196</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43604</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4526</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42046</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40762</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38393</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42144</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41117</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39109</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42265</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44119</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.49096</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.00739</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.01174</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26273</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.01229</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.03449</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.10563</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.0072</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.22364</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.03106</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.12755</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.15961</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.20936</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21494</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.19854</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.02203</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.03043</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.04189</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.22417</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20622</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.47548</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.51367</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73353</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.0801</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39496</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.9428500000000001</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43725</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.65998</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.82221</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.43101</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.15669</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.73087</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.07621</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.23993</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6412100000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.6926599999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.25337</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.04131</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87317</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.798</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7589600000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51961</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48099</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47158</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42617</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.71231</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.78057</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8747</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.92148</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.4965</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50527</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5055299999999999</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48761</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40064</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37853</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42168</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.9739099999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.81757</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.90088</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46886</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.45451</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37763</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50754</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35703</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.29036</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.27121</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.2103</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.66625</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.87002</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.20213</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.8478300000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.78604</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.32258</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.45043</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.81763</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.99264</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.09628</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.41719</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.46502</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.43147</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5028899999999999</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.80914</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.63271</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7726499999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.79089</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.15887</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24744</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18958</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8550399999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20334</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10435</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25731</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03443</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.08941</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.6447000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98238</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.90555</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9707899999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84377</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.9458300000000001</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7758400000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.74918</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.7689400000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78913</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4448</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37634</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35517</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33473</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51007</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48846</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49072</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41582</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39017</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42938</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44509</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39678</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36861</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39683</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47431</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43953</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.18694</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.01306</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.13374</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.06365999999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.09308</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.25088</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.7061499999999999</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.05821</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.62397</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.6994600000000001</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.51949</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.43184</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.81091</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.65626</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.61863</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.51437</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.47558</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.43169</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.47954</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.55489</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.56514</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5056499999999999</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2783</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61891</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.61129</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50657</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.60941</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.5720700000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.46366</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42448</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48524</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61358</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.6337200000000001</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5621900000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.75737</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6355599999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.55023</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.6009</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39803</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36214</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34208</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5280499999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49335</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38949</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35892</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45005</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38483</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38917</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41519</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.42614</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.3402</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.23831</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28773</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.24702</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.62607</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.6407</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46362</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37469</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.20585</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.5486799999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.42782</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6064700000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.3488</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.39661</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.49967</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.43347</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49888</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.51184</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.57043</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.44134</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55462</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47143</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.45752</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.49912</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.42182</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41652</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31913</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31855</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32116</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.42981</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38218</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31481</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.26642</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.1817</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3086</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.22571</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.20402</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15768</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.08673</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.22236</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.03441</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.34765</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.17931</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.14579</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.17668</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.01864</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00277</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.03388</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27883</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29358</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30143</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4678</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.50163</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35125</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6588099999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42498</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35767</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.3566</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35737</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33628</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10252</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04342</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04573</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01979</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.22485</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05855</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.22173</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.00554</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04395</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07898999999999999</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.07726000000000001</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36502</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33559</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31717</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21399</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49798</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8629</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29623</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.8875299999999999</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63161</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18711</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86803</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.49236</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33088</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03293</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79101</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.51888</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775599999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87388</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49317</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39992</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44996</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20702</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62188</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5383300000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42426</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44994</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.34513</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40348</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40039</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40065</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58735</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43532</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5963200000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.73633</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8788400000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46857</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.41928</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.58208</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87736</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.63007</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86211</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.8749600000000001</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.44198</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.69984</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60129</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33287</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34433</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31533</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29581</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3384</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41367</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45369</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41604</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35372</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91898</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46613</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.46682</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38148</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4011</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50171</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35853</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31508</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29073</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16444</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.33596</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19896</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31199</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.35222</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3178</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25567</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.33485</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.3863</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.45029</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40258</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5994299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89098</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.47303</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.16046</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70045</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79128</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65139</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58414</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45302</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.44068</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43874</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41573</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50282</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43482</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41427</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42966</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3969</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42418</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.4358</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41353</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40156</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39909</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.49536</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.3681</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36448</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24971</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16177</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.004019999999999999</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26163</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25539</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28298</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28873</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29644</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29202</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.32415</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.40456</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.36873</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36331</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.57198</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.84622</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46632</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37872</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.46426</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.3338</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3244</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.33934</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.30976</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32162</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3926</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.22592</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.13531</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.13341</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.27713</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.13914</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.13492</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.1333</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.13448</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.24545</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.13347</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25198</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.19786</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.11563</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.09554</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11116</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.11903</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.19299</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.13314</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27387</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39928</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3852</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40028</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39103</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39766</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.4513</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44321</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44378</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39712</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34844</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.53787</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46806</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42314</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39235</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37939</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3912</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38024</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35506</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34005</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.45002</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38031</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29517</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.23892</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.24298</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.32218</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31856</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.42181</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2897</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24216</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30781</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.50301</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.3464100000000001</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40492</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35447</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.37416</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.38638</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.27604</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38045</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35604</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4196</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36006</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.50351</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.51486</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.37458</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39834</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.22221</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.68588</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.85339</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.15769</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.82762</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.09397</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.61015</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.23887</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.40908</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.82076</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.44649</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.44853</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.79422</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.45516</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.93845</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.3016</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.02059</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.72284</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.14006</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.41101</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41913</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.63179</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.45557</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.43756</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6930599999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.7571599999999999</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.68235</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.57338</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.51019</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.24885</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3389</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34436</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.42915</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42563</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.35353</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34605</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.33521</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33197</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37965</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.37907</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38981</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.32853</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34462</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.31636</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.34806</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.45069</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36879</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35971</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35467</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36525</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.39808</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3492</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34959</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33952</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34935</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32477</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.35589</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.33037</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3498</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35877</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35872</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36106</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37954</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42545</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41263</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65662</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.7818200000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.28561</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45896</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.44405</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34493</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.3782</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37399</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.3632</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35804</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36171</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36779</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3818</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35839</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35378</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25748</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.12564</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.18947</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.41175</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.41333</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27718</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.20881</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.25045</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28225</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.28798</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.31349</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33305</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.42174</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40235</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64177</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5998300000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5981000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.49749</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.80787</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.48947</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.8313200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.43255</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48722</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42547</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37663</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36292</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.50146</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.596</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5284500000000001</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.7156399999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42405</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42476</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.42363</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39682</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41612</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41407</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.42507</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.42032</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40775</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.46329</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.46068</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.58061</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.46124</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.51113</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.48078</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.41986</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.50344</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.49881</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5833200000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.43651</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4328</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.8837699999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.38294</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.37586</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.38971</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.44513</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.5052300000000001</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.45968</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.52595</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.52735</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.5708</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.73072</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.87863</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.96727</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.68303</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.84321</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.71954</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.56292</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.87127</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.7727999999999999</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62582</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.67472</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.4967200000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.49521</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48877</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.48149</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.42446</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.43608</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.45093</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46626</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43661</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45549</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41826</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40554</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46932</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39961</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38272</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36585</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38157</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34711</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.49405</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42511</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42029</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.41044</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.09594</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17997</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.20416</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29574</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.42873</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43536</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.41957</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.45788</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.41024</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.41921</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.4049</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.42027</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37845</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.3964</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.38107</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.41136</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.37775</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.40179</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.40602</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.40744</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.38633</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.38767</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.36318</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.35591</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38481</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.24175</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.2238</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24425</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.24257</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15771</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.24765</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27817</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.15938</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.18052</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30965</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22716</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25341</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.26356</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.23134</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.2763</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2891</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39389</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4088</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.38958</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38775</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.38645</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38216</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.37906</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35085</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3418</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.33889</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.3358</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31401</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31092</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.21246</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01817</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00088</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04956</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14684</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02041</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03956</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04059</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04856</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0482</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.0291</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00054</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27292</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03872</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01791</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03618</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20132</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26384</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.36076</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.37705</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.44625</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31017</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.34473</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.83123</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.69756</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5357799999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.4419</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.37344</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.38765</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.36446</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.40789</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.44094</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.35756</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.39947</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.87478</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.9720800000000001</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8783200000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.83863</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.10029</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16267</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.22143</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.2083</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18682</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.0489</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.16315</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.01568</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.17855</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.01345</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.19186</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.02688</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.18522</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.20285</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25479</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.44938</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.38995</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.70294</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.85436</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.8582799999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.85641</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.47348</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9864400000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.85603</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.88724</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.8823799999999999</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8457</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.84387</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.84824</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.94524</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.85129</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.8782799999999999</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.85199</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.37853</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.8558</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.63859</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49915</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.50273</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.43211</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.40102</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.54316</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.50259</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.5248200000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.4147</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.38333</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.43508</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40836</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.72645</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.7271799999999999</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.25727</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.37347</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.9441499999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.8750399999999999</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.97213</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.98629</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2622</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.98414</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.34871</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.38822</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.43216</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.50154</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.87948</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.43504</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.68848</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.50361</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.4588</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.53571</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.35855</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.44418</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.45219</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.43213</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.40154</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35965</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38857</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.83462</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.6300800000000001</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.9113300000000001</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.7795599999999999</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30651</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35023</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.9136</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81667</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.43576</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.50398</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5461699999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.59748</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82738</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.49777</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.7875599999999999</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.6353300000000001</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.5056499999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.5062099999999999</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.44266</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.37407</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45819</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36838</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47794</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40098</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37881</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36956</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36634</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.36061</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34715</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.3996</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.38987</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36762</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33646</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34358</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.3253</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36825</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.38627</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.40457</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.38177</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.6513300000000001</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.72564</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.7121000000000001</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.80768</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.56448</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.36593</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.87202</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.08456</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.0378</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.9008700000000001</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.40221</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.8252999999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.33219</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.14274</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.04998</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.8486900000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.45492</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39911</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37706</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37268</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36984</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36594</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35156</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34136</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36377</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.38392</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.38288</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.35989</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36363</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.21009</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.29193</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.29847</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.19176</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.27322</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.25794</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.11514</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.1085</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27124</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14979</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17101</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.15207</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.19459</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.24865</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.2082</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.22631</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34736</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37613</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37814</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.36796</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.51381</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.46639</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45315</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41302</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38162</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.36732</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.35954</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38015</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.03441</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.40982</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.92948</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.60453</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43571</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.37697</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.41879</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.38281</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3791600000000001</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.37844</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37225</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36937</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36514</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35683</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37027</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>1.00731</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.00103</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.57178</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9829</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.36918</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.07011</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.92565</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.37315</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.54908</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.55871</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>1.308</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.9647100000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.93367</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.9712799999999999</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.99207</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.39009</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.40668</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.37305</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39085</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.39106</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39578</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.39863</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41753</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39706</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36789</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38269</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38101</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36887</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35426</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36388</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.36432</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.36685</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.35909</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.35684</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31515</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31534</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17469</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30856</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.1444</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19667</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.09883</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2886</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.02189</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.09132</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.17658</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.22012</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.16335</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.11535</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.25512</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.20941</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22496</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15404</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.32545</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30562</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10176</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.32994</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.22335</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19656</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1437</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.27409</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.31133</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36324</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36631</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.38496</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.40896</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38771</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36852</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.39262</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.40566</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48024</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.3941</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38642</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.3911</v>
       </c>
     </row>
   </sheetData>
